--- a/artfynd/A 8468-2023 artfynd.xlsx
+++ b/artfynd/A 8468-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8468-2023 artfynd.xlsx
+++ b/artfynd/A 8468-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106036006</v>
+        <v>106035853</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stensundet, Ög</t>
+          <t>Väderholmen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570211.9751075872</v>
+        <v>570254</v>
       </c>
       <c r="R2" t="n">
-        <v>6506294.347909063</v>
+        <v>6506213</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,51 +773,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106035690</v>
+        <v>106036006</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken, Ög</t>
+          <t>Stensundet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570425.4875964411</v>
+        <v>570212</v>
       </c>
       <c r="R3" t="n">
-        <v>6506324.725158918</v>
+        <v>6506294</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +864,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Eva Siljeholm, Olle Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -904,12 +874,7 @@
         <v>106035979</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570202.8234165048</v>
+        <v>570203</v>
       </c>
       <c r="R4" t="n">
-        <v>6506310.818959477</v>
+        <v>6506311</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,51 +974,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106035853</v>
+        <v>106035690</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väderholmen, Ög</t>
+          <t>Falkviken, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570254.0805891027</v>
+        <v>570426</v>
       </c>
       <c r="R5" t="n">
-        <v>6506212.445755226</v>
+        <v>6506324</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,19 +1043,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1065,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1135,12 +1075,7 @@
         <v>106035708</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570377.7656845455</v>
+        <v>570377</v>
       </c>
       <c r="R6" t="n">
-        <v>6506313.982889709</v>
+        <v>6506314</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,19 +1141,9 @@
           <t>2023-01-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 8468-2023 artfynd.xlsx
+++ b/artfynd/A 8468-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106035853</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106036006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106035979</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106035690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106035708</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>